--- a/results/Int All Data -1.0/Rando_7_permute.xlsx
+++ b/results/Int All Data -1.0/Rando_7_permute.xlsx
@@ -440,977 +440,977 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8970045680918861</v>
+        <v>0.8934734946455585</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8997558052505423</v>
+        <v>0.885646512112628</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8986078609708419</v>
+        <v>0.8884713708696901</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8986078609708419</v>
+        <v>0.8874856704341977</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8979316475763691</v>
+        <v>0.8881918851234631</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8979316475763691</v>
+        <v>0.8887658572633135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8989909696102674</v>
+        <v>0.8886922356649076</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8919860620300455</v>
+        <v>0.8844699481767109</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8990468272841249</v>
+        <v>0.885043920316561</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9057258655373548</v>
+        <v>0.893945225530786</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9055050007421372</v>
+        <v>0.8964169769432154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.906137593832997</v>
+        <v>0.8964169769432154</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9068438085222625</v>
+        <v>0.8952254123599018</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.902753763583481</v>
+        <v>0.8931067682921052</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.902753763583481</v>
+        <v>0.8964319775906118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8896151702336628</v>
+        <v>0.9070838188806043</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.890674492267561</v>
+        <v>0.9068043331343774</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8899682775782954</v>
+        <v>0.9073633046268312</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8848039099582192</v>
+        <v>0.9033318806390591</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.883744587924321</v>
+        <v>0.9040380953283247</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8818318080043455</v>
+        <v>0.9083490050623237</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8819640505537607</v>
+        <v>0.9072896830284254</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8734894742825743</v>
+        <v>0.9224732988476345</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8667804347345517</v>
+        <v>0.9224732988476345</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8662214632420978</v>
+        <v>0.9200165480826015</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8696789150900197</v>
+        <v>0.9200165480826015</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8696789150900197</v>
+        <v>0.9200165480826015</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.870458751377691</v>
+        <v>0.9196634407379687</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8644273068627173</v>
+        <v>0.9088043536615791</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8617496913024667</v>
+        <v>0.9119250804508405</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8744465550618501</v>
+        <v>0.9127635376895213</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8760648485882022</v>
+        <v>0.9031410171386345</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8672071636775902</v>
+        <v>0.9028465307450111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8676925135716383</v>
+        <v>0.9039058527789094</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8588648299558191</v>
+        <v>0.9039058527789094</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8163883257066884</v>
+        <v>0.9032732596880497</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8133576028018051</v>
+        <v>0.906230360994527</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8136070872532393</v>
+        <v>0.9037436089347014</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8088108276251922</v>
+        <v>0.9026106653023973</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8225970147132666</v>
+        <v>0.9017872087111127</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8186392123239004</v>
+        <v>0.900786507628224</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.826760681250454</v>
+        <v>0.9014927223174896</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8279958661373807</v>
+        <v>0.8990945925034659</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8269365441034824</v>
+        <v>0.8999330497421467</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8182561036844749</v>
+        <v>0.8990945925034659</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.817461266749407</v>
+        <v>0.8984033784615968</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8159615967636498</v>
+        <v>0.8866022112533278</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8159615967636498</v>
+        <v>0.88789739872984</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8159615967636498</v>
+        <v>0.888265506721869</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8180066192330406</v>
+        <v>0.8851311609237873</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8185219704218814</v>
+        <v>0.8858373756130528</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8140788181384671</v>
+        <v>0.8763770989063738</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8154762468696017</v>
+        <v>0.8794514421148703</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8174912680441998</v>
+        <v>0.8797309278610972</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8425032685621169</v>
+        <v>0.8828788926679993</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8482416083220434</v>
+        <v>0.8762434747183826</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.866588189595551</v>
+        <v>0.8769346887602517</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8635574666906678</v>
+        <v>0.8777881466463289</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8563194569449839</v>
+        <v>0.8796273049678986</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8544066770250085</v>
+        <v>0.8223311479758599</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8538913258361677</v>
+        <v>0.823050981673946</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8538913258361677</v>
+        <v>0.823050981673946</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8210209598519516</v>
+        <v>0.8224920101814921</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8273768920553413</v>
+        <v>0.8207264734583282</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8209323376061493</v>
+        <v>0.8227414946329263</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8401909977167437</v>
+        <v>0.801024702118723</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8257135965868001</v>
+        <v>0.8017309168079886</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8245956536018924</v>
+        <v>0.8013778094633558</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8219780406312271</v>
+        <v>0.8017309168079886</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8178593760362289</v>
+        <v>0.7804708545316166</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8157843522720454</v>
+        <v>0.7796323972929358</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8162847028134899</v>
+        <v>0.7799118830391627</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7826795024837914</v>
+        <v>0.7799118830391627</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7833857171730569</v>
+        <v>0.7741299229756231</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7833857171730569</v>
+        <v>0.775895459698787</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7843127966575399</v>
+        <v>0.7621842758476944</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7812084521542508</v>
+        <v>0.765141377154172</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7809289664080239</v>
+        <v>0.7524881336984017</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7810025880064297</v>
+        <v>0.7252102459158764</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.776986164666054</v>
+        <v>0.700993082333027</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7752792488938997</v>
+        <v>0.7036706978932775</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7742199268600014</v>
+        <v>0.726122324752963</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.778147727954575</v>
+        <v>0.7153668605697719</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7773678916669036</v>
+        <v>0.7153668605697719</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7753378698449092</v>
+        <v>0.6227641140301845</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7753378698449092</v>
+        <v>0.6227641140301845</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.773925440466378</v>
+        <v>0.6075068766125695</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7518855419023347</v>
+        <v>0.6138628088159594</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7263731908429732</v>
+        <v>0.6145690235052249</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7263731908429732</v>
+        <v>0.6128034867820611</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7365846841811068</v>
+        <v>0.6110379500588973</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7405424865704731</v>
+        <v>0.6161586973753604</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7576416455868096</v>
+        <v>0.6153202401366796</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7576416455868096</v>
+        <v>0.6133338386182983</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7563028378066843</v>
+        <v>0.6133338386182983</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6349483898778789</v>
+        <v>0.6160850757769546</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5028248587570622</v>
+        <v>0.6104203576154339</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5017655367231638</v>
+        <v>0.5986055713983446</v>
       </c>
     </row>
     <row r="100">
@@ -1420,543 +1420,543 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5007062146892656</v>
+        <v>0.5849666275070819</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5849666275070819</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.595559847846065</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5940737968691281</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.6138478081685631</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.6173052600164849</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4997941358521789</v>
+        <v>0.6091101694915254</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5</v>
+        <v>0.5996498927848465</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5</v>
+        <v>0.6021952657956817</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5</v>
+        <v>0.5921610169491526</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5921610169491526</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5921610169491526</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.6120822714453993</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.6257948369350677</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.603416831673788</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.606594797775483</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5000736215984058</v>
+        <v>0.6093460349341393</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.6326074993762889</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5193036620527833</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5195831477990103</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5</v>
+        <v>0.5195831477990103</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5</v>
+        <v>0.5139334302848859</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5</v>
+        <v>0.5139334302848859</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5</v>
+        <v>0.5101228710923313</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5</v>
+        <v>0.5060914471045592</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5</v>
+        <v>0.5122265145127316</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5</v>
+        <v>0.5063559322033898</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5007062146892656</v>
+        <v>0.5102401129943502</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5102401129943502</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5</v>
+        <v>0.5144187801789341</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5</v>
+        <v>0.5198626335452372</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5</v>
+        <v>0.5179498536252617</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5</v>
+        <v>0.5113730566266544</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5</v>
+        <v>0.5106232216337757</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.5106232216337757</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.5121092726107127</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5</v>
+        <v>0.5121092726107127</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5</v>
+        <v>0.5026339952566373</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.5019864015183814</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.500927079484483</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5016332941737486</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5012801868291158</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5048412615702362</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.504150047528367</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.504150047528367</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5004731125238037</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.4984867110054224</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.4984417090632333</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5004267289430386</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B156" t="n">
